--- a/projetos/OBRA_TMULT/04_PRODUCAO_E_AVANCO/HISTOGRAMA_EQUIPAMENTOS_TMULT.xlsx
+++ b/projetos/OBRA_TMULT/04_PRODUCAO_E_AVANCO/HISTOGRAMA_EQUIPAMENTOS_TMULT.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OBRA TMULT (PORTO DO AÇU) — HISTOGRAMA DE EQUIPAMENTOS &amp; INFRAESTRUTURA DE CANTEIRO</t>
+          <t>TMULT — HISTOGRAMA DE EQUIPAMENTOS &amp; INFRAESTRUTURA DE CANTEIRO</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Dimensionamento de Maquinário, Andaimes e Módulos Habitáveis NR-18 ao longo dos 6 Meses de Execução</t>
+          <t>Dimensionamento de Maquinário, Andaimes e Módulos Habitáveis ao longo dos 6 Meses de Execução</t>
         </is>
       </c>
     </row>
